--- a/phases/0-setup/트리플 여행 추천 경로.xlsx
+++ b/phases/0-setup/트리플 여행 추천 경로.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rlaeh\OneDrive\바탕 화면\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rlaeh\OneDrive\바탕 화면\Projects\travel\phases\0-setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0912A3F5-1D97-4A2B-9B68-0BFA79708D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF97CD82-5941-4D68-8389-61297A5C8C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5915F513-A29B-43AA-A9A0-106912CF4A7E}"/>
+    <workbookView xWindow="10932" yWindow="432" windowWidth="10512" windowHeight="11508" xr2:uid="{5915F513-A29B-43AA-A9A0-106912CF4A7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
